--- a/test_support/fixtures/xlsx/xlsx-error-ref.xlsx
+++ b/test_support/fixtures/xlsx/xlsx-error-ref.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Word Project\test_support\fixtures\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BB7001-B260-4A89-A40E-9CEDF7647DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A238C604-1252-45A2-A272-D4B4FEB9534B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
